--- a/Fairway_Golf_Club_Phase1_Budget_200K.xlsx
+++ b/Fairway_Golf_Club_Phase1_Budget_200K.xlsx
@@ -1,25 +1,32 @@
 
-<file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2">
-  <fileVersion appName="Calc" lowestEdited="4"/>
-  <workbookPr backupFile="false" showObjects="all" date1904="false"/>
-  <workbookProtection/>
-  <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
-  </bookViews>
-  <sheets>
-    <sheet name="Budget Summary" sheetId="1" state="visible" r:id="rId3"/>
-  </sheets>
-  <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
-  <extLst>
-    <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
-      <loext:extCalcPr stringRefSyntax="ExcelA1"/>
-    </ext>
-  </extLst>
-</workbook>
+<file path=docProps\app.xml><?xml version="1.0" encoding="utf-8"?>
+<Properties xmlns="http://schemas.openxmlformats.org/officeDocument/2006/extended-properties" xmlns:vt="http://schemas.openxmlformats.org/officeDocument/2006/docPropsVTypes">
+  <Template/>
+  <TotalTime>0</TotalTime>
+  <Application>LibreOffice/26.2.4.2$Linux_AARCH64 LibreOffice_project/620$Build-2</Application>
+  <AppVersion>15.0000</AppVersion>
+</Properties>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=docProps\core.xml><?xml version="1.0" encoding="utf-8"?>
+<cp:coreProperties xmlns:cp="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:dcmitype="http://purl.org/dc/dcmitype/" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance">
+  <dcterms:created xsi:type="dcterms:W3CDTF">2026-07-03T01:03:37Z</dcterms:created>
+  <dc:creator>openpyxl</dc:creator>
+  <dc:description/>
+  <dc:language>en-US</dc:language>
+  <cp:lastModifiedBy/>
+  <dcterms:modified xsi:type="dcterms:W3CDTF">2026-07-03T01:03:37Z</dcterms:modified>
+  <cp:revision>0</cp:revision>
+  <dc:subject/>
+  <dc:title/>
+</cp:coreProperties>
+</file>
+
+<file path=docProps\custom.xml><?xml version="1.0" encoding="utf-8"?>
+<Properties xmlns="http://schemas.openxmlformats.org/officeDocument/2006/custom-properties" xmlns:vt="http://schemas.openxmlformats.org/officeDocument/2006/docPropsVTypes"/>
+</file>
+
+<file path=xl\sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="115">
   <si>
     <t xml:space="preserve">FAIRWAY GOLF CLUB</t>
@@ -369,7 +376,7 @@
 </sst>
 </file>
 
-<file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl\styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="2">
     <numFmt numFmtId="164" formatCode="General"/>
@@ -726,7 +733,7 @@
 </styleSheet>
 </file>
 
-<file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl\theme\theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
@@ -901,7 +908,27 @@
 </a:theme>
 </file>
 
-<file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl\workbook.xml><?xml version="1.0" encoding="utf-8"?>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2">
+  <fileVersion appName="Calc" lowestEdited="4"/>
+  <workbookPr backupFile="false" showObjects="all" date1904="false"/>
+  <workbookProtection/>
+  <bookViews>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
+  </bookViews>
+  <sheets>
+    <sheet name="Budget Summary" sheetId="1" state="visible" r:id="rId3"/>
+  </sheets>
+  <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001" fullCalcOnLoad="1"/>
+  <extLst>
+    <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
+      <loext:extCalcPr stringRefSyntax="ExcelA1"/>
+    </ext>
+  </extLst>
+</workbook>
+</file>
+
+<file path=xl\worksheets\sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
@@ -968,13 +995,15 @@
         <v>10</v>
       </c>
       <c r="C9" s="8" t="n">
-        <v>4000</v>
+        <v>7000</v>
       </c>
       <c r="D9" s="9" t="n">
         <v>7000</v>
       </c>
-      <c r="E9" s="10" t="s">
-        <v>11</v>
+      <c r="E9" s="10" t="inlineStr">
+        <is>
+          <t>Upgraded to BenQ cinema-grade ($3.5K ea) — full premium spec</t>
+        </is>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -982,13 +1011,15 @@
         <v>12</v>
       </c>
       <c r="C10" s="8" t="n">
-        <v>1600</v>
+        <v>3000</v>
       </c>
       <c r="D10" s="9" t="n">
         <v>3000</v>
       </c>
-      <c r="E10" s="10" t="s">
-        <v>13</v>
+      <c r="E10" s="10" t="inlineStr">
+        <is>
+          <t>Upgraded to full premium screens (10,500 ea)</t>
+        </is>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -996,13 +1027,15 @@
         <v>14</v>
       </c>
       <c r="C11" s="8" t="n">
-        <v>1200</v>
+        <v>4000</v>
       </c>
       <c r="D11" s="9" t="n">
         <v>4000</v>
       </c>
-      <c r="E11" s="10" t="s">
-        <v>15</v>
+      <c r="E11" s="10" t="inlineStr">
+        <is>
+          <t>Upgraded to pre-fab enclosure frames</t>
+        </is>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1010,13 +1043,15 @@
         <v>16</v>
       </c>
       <c r="C12" s="8" t="n">
-        <v>4000</v>
+        <v>6000</v>
       </c>
       <c r="D12" s="9" t="n">
         <v>6000</v>
       </c>
-      <c r="E12" s="10" t="s">
-        <v>17</v>
+      <c r="E12" s="10" t="inlineStr">
+        <is>
+          <t>Upgraded to full premium PC build</t>
+        </is>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1066,13 +1101,15 @@
         <v>24</v>
       </c>
       <c r="C16" s="8" t="n">
-        <v>800</v>
+        <v>1600</v>
       </c>
       <c r="D16" s="9" t="n">
         <v>1600</v>
       </c>
-      <c r="E16" s="10" t="s">
-        <v>25</v>
+      <c r="E16" s="10" t="inlineStr">
+        <is>
+          <t>Upgraded to commercial-grade displays</t>
+        </is>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1085,7 +1122,7 @@
         <v>27</v>
       </c>
       <c r="C19" s="8" t="n">
-        <v>8000</v>
+        <v>12000</v>
       </c>
       <c r="D19" s="9" t="n">
         <v>12000</v>
@@ -1099,13 +1136,15 @@
         <v>29</v>
       </c>
       <c r="C20" s="8" t="n">
-        <v>2400</v>
+        <v>8000</v>
       </c>
       <c r="D20" s="9" t="n">
         <v>8000</v>
       </c>
-      <c r="E20" s="10" t="s">
-        <v>30</v>
+      <c r="E20" s="10" t="inlineStr">
+        <is>
+          <t>Upgraded to commercial acoustic treatment ($4K/bay)</t>
+        </is>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1113,13 +1152,15 @@
         <v>31</v>
       </c>
       <c r="C21" s="8" t="n">
-        <v>3200</v>
+        <v>5000</v>
       </c>
       <c r="D21" s="9" t="n">
         <v>5000</v>
       </c>
-      <c r="E21" s="10" t="s">
-        <v>32</v>
+      <c r="E21" s="10" t="inlineStr">
+        <is>
+          <t>Upgraded to installed premium turf</t>
+        </is>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1127,7 +1168,7 @@
         <v>33</v>
       </c>
       <c r="C22" s="8" t="n">
-        <v>3000</v>
+        <v>5000</v>
       </c>
       <c r="D22" s="9" t="n">
         <v>5000</v>
@@ -1141,7 +1182,7 @@
         <v>35</v>
       </c>
       <c r="C23" s="8" t="n">
-        <v>5000</v>
+        <v>8000</v>
       </c>
       <c r="D23" s="9" t="n">
         <v>8000</v>
@@ -1155,7 +1196,7 @@
         <v>37</v>
       </c>
       <c r="C24" s="8" t="n">
-        <v>4000</v>
+        <v>6000</v>
       </c>
       <c r="D24" s="9" t="n">
         <v>6000</v>
@@ -1169,7 +1210,7 @@
         <v>39</v>
       </c>
       <c r="C25" s="8" t="n">
-        <v>1500</v>
+        <v>3000</v>
       </c>
       <c r="D25" s="9" t="n">
         <v>3000</v>
@@ -1183,13 +1224,15 @@
         <v>41</v>
       </c>
       <c r="C26" s="8" t="n">
-        <v>600</v>
+        <v>2000</v>
       </c>
       <c r="D26" s="9" t="n">
         <v>2000</v>
       </c>
-      <c r="E26" s="10" t="s">
-        <v>42</v>
+      <c r="E26" s="10" t="inlineStr">
+        <is>
+          <t>Upgraded to custom LED installation</t>
+        </is>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1658,7 +1701,7 @@
       </c>
       <c r="C70" s="13" t="n">
         <f aca="false">SUM(C8,C9,C10,C11,C12,C13,C14,C15,C16,C19,C20,C21,C22,C23,C24,C25,C26,C29,C30,C31,C32,C33,C34,C35,C36,C37,C38,C39,C40,C43,C44,C45,C46,C47,C50,C51,C52,C53,C54,C55,C58,C59,C60,C63,C64,C65,C66,C67)</f>
-        <v>123300</v>
+        <v>154600</v>
       </c>
       <c r="D70" s="14" t="n">
         <f aca="false">SUM(D8,D9,D10,D11,D12,D13,D14,D15,D16,D19,D20,D21,D22,D23,D24,D25,D26,D29,D30,D31,D32,D33,D34,D35,D36,D37,D38,D39,D40,D43,D44,D45,D46,D47,D50,D51,D52,D53,D54,D55,D58,D59,D60,D63,D64,D65,D66,D67)</f>
@@ -1671,7 +1714,7 @@
       </c>
       <c r="C71" s="16" t="n">
         <f aca="false">C70*0.1</f>
-        <v>12330</v>
+        <v>15460</v>
       </c>
       <c r="D71" s="14" t="n">
         <f aca="false">D70*0.1</f>
@@ -1684,7 +1727,7 @@
       </c>
       <c r="C72" s="18" t="n">
         <f aca="false">C70+C71</f>
-        <v>135630</v>
+        <v>170060</v>
       </c>
       <c r="D72" s="19" t="n">
         <f aca="false">D70+D71</f>
@@ -1698,7 +1741,7 @@
       </c>
       <c r="C73" s="21" t="n">
         <f aca="false">D72-C72</f>
-        <v>131230</v>
+        <v>96800</v>
       </c>
     </row>
     <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
